--- a/OneDrive/Documents/UiPath/StockTrackerBot/Config.xlsx
+++ b/OneDrive/Documents/UiPath/StockTrackerBot/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dovra\OneDrive\Documents\UiPath\StockTrackerBot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72491406-9E0A-4E1B-9469-17D05E1CA742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71764719-5D7E-4B7F-B967-AAD1C58DF7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5205" yWindow="3555" windowWidth="16395" windowHeight="7898" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="32">
   <si>
     <t>Ticker</t>
   </si>
@@ -104,9 +104,6 @@
     <t>Alerted(Y/N)</t>
   </si>
   <si>
-    <t>5BGL2D8C5LBZX7HP</t>
-  </si>
-  <si>
     <t xml:space="preserve">API Key </t>
   </si>
   <si>
@@ -114,6 +111,12 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>RSM4PWB3J26MNP8Q</t>
   </si>
 </sst>
 </file>
@@ -437,10 +440,10 @@
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -458,7 +461,7 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>4</v>
@@ -572,7 +575,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F414F2-D242-4B1E-84E0-5520CB148B8D}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
@@ -600,323 +603,899 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B34" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C34" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B58" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58">
+        <v>229.03</v>
+      </c>
+      <c r="E58">
+        <v>-0.1961</v>
+      </c>
+      <c r="F58" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D59">
+        <v>229.03</v>
+      </c>
+      <c r="E59">
+        <v>-0.1961</v>
+      </c>
+      <c r="F59" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B60" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C60" t="s">
         <v>11</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D60">
+        <v>229.03</v>
+      </c>
+      <c r="E60">
+        <v>-0.1961</v>
+      </c>
+      <c r="F60" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B61" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C61" t="s">
         <v>13</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D61">
+        <v>229.03</v>
+      </c>
+      <c r="E61">
+        <v>-0.1961</v>
+      </c>
+      <c r="F61" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B62" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C62" t="s">
         <v>15</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D62">
+        <v>229.03</v>
+      </c>
+      <c r="E62">
+        <v>-0.1961</v>
+      </c>
+      <c r="F62" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B63" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C63" t="s">
         <v>17</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D63">
+        <v>229.03</v>
+      </c>
+      <c r="E63">
+        <v>-0.1961</v>
+      </c>
+      <c r="F63" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B64" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C64" t="s">
         <v>19</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D64">
+        <v>229.03</v>
+      </c>
+      <c r="E64">
+        <v>-0.1961</v>
+      </c>
+      <c r="F64" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B65" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C65" t="s">
         <v>21</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="D65">
+        <v>229.03</v>
+      </c>
+      <c r="E65">
+        <v>-0.1961</v>
+      </c>
+      <c r="F65" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B66" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C66" t="s">
         <v>6</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="D66">
+        <v>229.03</v>
+      </c>
+      <c r="E66">
+        <v>-0.1961</v>
+      </c>
+      <c r="F66" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B67" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C67" t="s">
         <v>9</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="D67">
+        <v>229.03</v>
+      </c>
+      <c r="E67">
+        <v>-0.1961</v>
+      </c>
+      <c r="F67" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B68" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="C68" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="D68">
+        <v>229.03</v>
+      </c>
+      <c r="E68">
+        <v>-0.1961</v>
+      </c>
+      <c r="F68" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B69" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="C69" t="s">
         <v>13</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="D69">
+        <v>229.03</v>
+      </c>
+      <c r="E69">
+        <v>-0.1961</v>
+      </c>
+      <c r="F69" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B70" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="C70" t="s">
         <v>15</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="D70">
+        <v>229.03</v>
+      </c>
+      <c r="E70">
+        <v>-0.1961</v>
+      </c>
+      <c r="F70" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B71" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="C71" t="s">
         <v>17</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="D71">
+        <v>229.03</v>
+      </c>
+      <c r="E71">
+        <v>-0.1961</v>
+      </c>
+      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B72" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="C72" t="s">
         <v>19</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="D72">
+        <v>229.03</v>
+      </c>
+      <c r="E72">
+        <v>-0.1961</v>
+      </c>
+      <c r="F72" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B73" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="C73" t="s">
         <v>21</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" t="s">
-        <v>30</v>
+      <c r="D73">
+        <v>229.03</v>
+      </c>
+      <c r="E73">
+        <v>-0.1961</v>
+      </c>
+      <c r="F73" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/OneDrive/Documents/UiPath/StockTrackerBot/Config.xlsx
+++ b/OneDrive/Documents/UiPath/StockTrackerBot/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dovra\OneDrive\Documents\UiPath\StockTrackerBot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71764719-5D7E-4B7F-B967-AAD1C58DF7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442AF43C-1B76-473F-9B8B-1A97C639F09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="32">
   <si>
     <t>Ticker</t>
   </si>
@@ -107,9 +107,6 @@
     <t xml:space="preserve">API Key </t>
   </si>
   <si>
-    <t>dovraneymirov171@gmail.com</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -117,6 +114,9 @@
   </si>
   <si>
     <t>RSM4PWB3J26MNP8Q</t>
+  </si>
+  <si>
+    <t>dovran.eymirov@ktu.edu</t>
   </si>
 </sst>
 </file>
@@ -440,10 +440,10 @@
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -575,7 +575,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F414F2-D242-4B1E-84E0-5520CB148B8D}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -815,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
@@ -1075,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
@@ -1183,7 +1183,7 @@
         <v>46148</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
         <v>6</v>
@@ -1195,7 +1195,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -1203,7 +1203,7 @@
         <v>46148</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
@@ -1215,7 +1215,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
@@ -1223,7 +1223,7 @@
         <v>46148</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
         <v>11</v>
@@ -1235,7 +1235,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -1243,7 +1243,7 @@
         <v>46148</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
@@ -1255,7 +1255,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
@@ -1263,7 +1263,7 @@
         <v>46148</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
         <v>15</v>
@@ -1275,7 +1275,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
@@ -1283,7 +1283,7 @@
         <v>46148</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
@@ -1295,7 +1295,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
@@ -1303,7 +1303,7 @@
         <v>46148</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
         <v>19</v>
@@ -1315,7 +1315,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F64" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -1323,7 +1323,7 @@
         <v>46148</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
         <v>21</v>
@@ -1335,7 +1335,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -1343,7 +1343,7 @@
         <v>46148</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s">
         <v>6</v>
@@ -1355,7 +1355,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F66" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -1363,7 +1363,7 @@
         <v>46148</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
@@ -1375,7 +1375,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F67" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -1383,7 +1383,7 @@
         <v>46148</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -1395,7 +1395,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F68" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -1403,7 +1403,7 @@
         <v>46148</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
@@ -1415,7 +1415,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F69" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -1423,7 +1423,7 @@
         <v>46148</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
@@ -1435,7 +1435,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -1443,7 +1443,7 @@
         <v>46148</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
@@ -1455,7 +1455,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F71" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -1463,7 +1463,7 @@
         <v>46148</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C72" t="s">
         <v>19</v>
@@ -1475,7 +1475,7 @@
         <v>-0.1961</v>
       </c>
       <c r="F72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -1483,7 +1483,7 @@
         <v>46148</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C73" t="s">
         <v>21</v>
@@ -1495,7 +1495,167 @@
         <v>-0.1961</v>
       </c>
       <c r="F73" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B81" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/OneDrive/Documents/UiPath/StockTrackerBot/Config.xlsx
+++ b/OneDrive/Documents/UiPath/StockTrackerBot/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dovra\OneDrive\Documents\UiPath\StockTrackerBot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442AF43C-1B76-473F-9B8B-1A97C639F09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E031EF8-1019-4229-AB33-A4DC892676C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="32">
   <si>
     <t>Ticker</t>
   </si>
@@ -575,7 +575,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F414F2-D242-4B1E-84E0-5520CB148B8D}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
@@ -1658,6 +1658,486 @@
         <v>28</v>
       </c>
     </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82">
+        <v>287.51</v>
+      </c>
+      <c r="E82">
+        <v>1.1718</v>
+      </c>
+      <c r="F82" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83">
+        <v>413.96</v>
+      </c>
+      <c r="E83">
+        <v>0.62719999999999998</v>
+      </c>
+      <c r="F83" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84">
+        <v>398.04</v>
+      </c>
+      <c r="E84">
+        <v>2.4741</v>
+      </c>
+      <c r="F84" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85">
+        <v>274.99</v>
+      </c>
+      <c r="E85">
+        <v>0.52639999999999998</v>
+      </c>
+      <c r="F85" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86">
+        <v>398.73</v>
+      </c>
+      <c r="E86">
+        <v>2.4039000000000001</v>
+      </c>
+      <c r="F86" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87">
+        <v>207.83</v>
+      </c>
+      <c r="E87">
+        <v>5.7659000000000002</v>
+      </c>
+      <c r="F87" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B88" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88">
+        <v>314.89999999999998</v>
+      </c>
+      <c r="E88">
+        <v>1.7776000000000001</v>
+      </c>
+      <c r="F88" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89">
+        <v>88.27</v>
+      </c>
+      <c r="E89">
+        <v>0.43240000000000001</v>
+      </c>
+      <c r="F89" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90">
+        <v>287.51</v>
+      </c>
+      <c r="E90">
+        <v>1.1718</v>
+      </c>
+      <c r="F90" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B91" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91">
+        <v>413.96</v>
+      </c>
+      <c r="E91">
+        <v>0.62719999999999998</v>
+      </c>
+      <c r="F91" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B92" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92">
+        <v>398.04</v>
+      </c>
+      <c r="E92">
+        <v>2.4741</v>
+      </c>
+      <c r="F92" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B93" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93">
+        <v>274.99</v>
+      </c>
+      <c r="E93">
+        <v>0.52639999999999998</v>
+      </c>
+      <c r="F93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B94" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94">
+        <v>398.73</v>
+      </c>
+      <c r="E94">
+        <v>2.4039000000000001</v>
+      </c>
+      <c r="F94" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95">
+        <v>207.83</v>
+      </c>
+      <c r="E95">
+        <v>5.7659000000000002</v>
+      </c>
+      <c r="F95" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96">
+        <v>314.89999999999998</v>
+      </c>
+      <c r="E96">
+        <v>1.7776000000000001</v>
+      </c>
+      <c r="F96" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B97" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97">
+        <v>88.27</v>
+      </c>
+      <c r="E97">
+        <v>0.43240000000000001</v>
+      </c>
+      <c r="F97" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98">
+        <v>287.51</v>
+      </c>
+      <c r="E98">
+        <v>1.1718</v>
+      </c>
+      <c r="F98" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B99" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99">
+        <v>413.96</v>
+      </c>
+      <c r="E99">
+        <v>0.62719999999999998</v>
+      </c>
+      <c r="F99" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100">
+        <v>398.04</v>
+      </c>
+      <c r="E100">
+        <v>2.4741</v>
+      </c>
+      <c r="F100" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101">
+        <v>274.99</v>
+      </c>
+      <c r="E101">
+        <v>0.52639999999999998</v>
+      </c>
+      <c r="F101" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B102" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102">
+        <v>398.73</v>
+      </c>
+      <c r="E102">
+        <v>2.4039000000000001</v>
+      </c>
+      <c r="F102" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103">
+        <v>207.83</v>
+      </c>
+      <c r="E103">
+        <v>5.7659000000000002</v>
+      </c>
+      <c r="F103" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B104" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104">
+        <v>314.89999999999998</v>
+      </c>
+      <c r="E104">
+        <v>1.7776000000000001</v>
+      </c>
+      <c r="F104" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105">
+        <v>88.27</v>
+      </c>
+      <c r="E105">
+        <v>0.43240000000000001</v>
+      </c>
+      <c r="F105" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
